--- a/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-1 地球的水　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上5-1 地球的水　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>地球水體的總稱是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>大致不變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>水圈</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>總稱</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地球上最多的水是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>海洋</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>淡水</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>海水(鹹水)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>約97.5%</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>淡水約佔多少？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>約2.5%</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>淡水少且多凍結,可直接用的更少</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>驅動蒸發</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>很少</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>水由液態變氣態是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>蒸發</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>逕流</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>水氣變回液態是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>逕流</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>凝結</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>成雲</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>雲中水落下是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>大致不變</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>降水</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>冰川與地下水</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>雨雪</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>水循環主要動力來自？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>太陽能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>逕流</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>蒸發</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>使水往低處流的是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>太陽能</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>下流</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>地球上鹹水主要存在於？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>驅動蒸發</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>降水</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>海洋</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>海水</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>水從地表蒸發需要什麼能量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>太陽能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>海洋</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>蒸發</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-1 地球的水　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上5-1 地球的水　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>水循環的順序？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>各環節間轉移不生不滅</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>太陽能蒸發、重力使水下流</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不透水面增加逕流增快</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>蒸發凝結降水逕流</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>過程</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>淡水多以什麼形式存在？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>驅動蒸發</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>冰川與地下水</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>大致不變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>儲存</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>地表水流回海洋稱？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>逕流</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>淡水</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>河川</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>水循環使水總量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>大致不變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>降水</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>海水能直接飲用嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>大致不變</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>含鹽</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>地下水屬淡水還鹹水？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>淡水</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>冰川與地下水</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>資源</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>太陽能在水循環的作用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>驅動蒸發</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>凝結形成什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>雲</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>淡水</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>冰川與地下水</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>水氣</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>雲是水氣經什麼作用形成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>凝結</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>海洋</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>降水</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>成雲</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>地下水屬於淡水還鹹水？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>淡水</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>水圈</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>驅動蒸發</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>資源</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上5-1 地球的水　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上5-1 地球的水　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何淡水資源顯得珍貴？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>淡水少且多凍結,可直接用的更少</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>含鹽需淡化成本高</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>各環節間轉移不生不滅</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>重複利用、減少浪費</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用水循環解釋為何水總量守恆？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>各環節間轉移總量不變</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>使可用淡水減少危害生態</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>淡水少且多凍結,可直接用的更少</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>蒸發凝結降水逕流</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分析水循環中太陽能與重力各扮演角色？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>太陽能蒸發、重力使水下流</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>淡水少且多凍結,可直接用的更少</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>含鹽需淡化成本高</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不透水面增加逕流增快</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>動力</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>水污染如何影響水資源？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不透水面增加逕流增快</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>短期增水長期減儲、海面上升</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>含鹽需淡化成本高</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>使可用淡水減少危害生態</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>污染</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>冰川融化對水資源與海平面影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>淡水少且多凍結,可直接用的更少</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>使可用淡水減少危害生態</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>蒸發凝結降水逕流</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>短期增水長期減儲、海面上升</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>氣候</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>都市化如何影響逕流？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>蒸發凝結降水逕流</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>不透水面增加逕流增快</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>各環節間轉移總量不變</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>太陽能蒸發、重力使水下流</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>人為</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何海水佔比高卻不易利用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>含鹽需淡化成本高</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>太陽能蒸發、重力使水下流</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>淡水少且多凍結,可直接用的更少</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>蒸發凝結降水逕流</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>限制</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>如何從生活節約水資源？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>各環節間轉移不生不滅</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>重複利用、減少浪費</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>各環節間轉移總量不變</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>短期增水長期減儲、海面上升</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何水循環使地球水總量大致不變？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不透水面增加逕流增快</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>各環節間轉移不生不滅</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>太陽能蒸發、重力使水下流</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>使可用淡水減少危害生態</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>冰川大量融化對海平面的影響？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>驅動蒸發</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>氣候</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>總稱</t>
+          <t>總稱：地球上所有的水,包括海洋河川冰川等,合起來稱為水圈</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>約97.5%</t>
+          <t>約97.5%：地球上絕大部分的水是海洋裡帶鹹味的鹹水</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>很少</t>
+          <t>很少：能喝能用的淡水只佔地球全部水量的一小部分,大約2.5%</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：水受熱從液體變成水氣飄到空中,叫做蒸發</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>成雲</t>
+          <t>成雲：空中的水氣遇冷變回小水滴,聚集起來就形成雲</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>雨雪</t>
+          <t>雨雪：雲裡的小水滴或冰晶變大變重後掉落,就是我們看到的雨或雪</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>蒸發：太陽提供熱能讓海洋河川的水蒸發,是水循環最主要的動力</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>下流</t>
+          <t>下流：地球的重力把水往低處拉,讓河水能一路流向大海</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>海水</t>
+          <t>海水：地球上的水絕大部分是含鹽分的海水,主要存在於海洋中,占地球水總量的大多數</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>蒸發：水要從液態變成水蒸氣蒸發到空中,需要吸收熱量,這個熱量主要來自太陽輻射的能量</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>過程</t>
+          <t>過程：水先蒸發變成水氣,水氣凝結成雲,雲降水落下,最後形成逕流流回大海</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>儲存</t>
+          <t>儲存：能喝的淡水裡,大部分都被凍結成冰川,或藏在地底下的地下水裡</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>河川</t>
+          <t>河川：雨水在地表匯集成河流,再一路流回海洋的過程叫逕流</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：水只是在海洋大氣陸地間不斷轉移位置,整體總量幾乎不會改變</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>含鹽</t>
+          <t>含鹽：海水裡含有大量鹽分,直接喝下去對身體不好,不能拿來飲用</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>資源</t>
+          <t>資源：地下水是雨水滲入地底儲存的,屬於可利用的淡水資源</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：太陽提供的熱能是讓水從液體蒸發成水氣的主要能量來源</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>水氣</t>
+          <t>水氣：空中的水氣遇到冷空氣凝結成小水滴,聚集在一起就變成雲</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>成雲</t>
+          <t>成雲：空氣中的水蒸氣遇冷後凝結成微小水滴或冰晶,聚集在空中就形成了雲</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>資源</t>
+          <t>資源：地下水是雨水滲入地層累積形成的,含鹽量很低,屬於淡水,是重要的淡水資源</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>稀有：淡水本來就只佔全部水量一小部分,其中大多又結冰在冰川裡,真正能直接取用的更是稀少</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：水只是不斷在蒸發、凝結、降水、逕流之間轉換位置,並沒有真的消失或增加</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>動力</t>
+          <t>動力：太陽能負責把水加熱蒸發送上天空,重力則負責把降下的雨水和河水拉往低處流動</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>污染：污染物混入水中讓原本能使用的淡水變得不能用,也會傷害水中的生物</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>氣候</t>
+          <t>氣候：冰川融化短時間內會多出一些水,但長期會讓淡水儲備減少,同時融化的水流入海洋讓海平面上升</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>人為</t>
+          <t>人為：都市裡鋪滿柏油水泥,雨水無法滲入地下,只能快速流走形成逕流,容易造成淹水</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>限制</t>
+          <t>限制：海水雖然數量最多,但要先把鹽分去除才能使用,這個淡化過程需要花費大量成本</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>行動：像是洗菜水拿來澆花、隨手關水龍頭,都能減少不必要的水資源浪費</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：水在蒸發、凝結、降水、逕流等各環節之間不斷循環轉移形態與位置,但水分子本身不會憑空消失或增加,所以地球水的總量大致維持不變</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>氣候</t>
+          <t>氣候：陸地上的冰川原本不算在海水裡,大量融化後多出來的水流入海洋,會使全球海平面上升</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上5-1_三種難度測驗卷.xlsx
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>淡水少且多凍結,可直接用的更少</t>
+          <t>大致不變</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>海水(鹹水)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>蒸發</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>驅動蒸發</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>逕流</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>海水(鹹水)</t>
+          <t>凝結</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>逕流</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>水圈</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>凝結</t>
+          <t>太陽能</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>降水</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
